--- a/InputData/ccs/CC/CCS Calculations.xlsx
+++ b/InputData/ccs/CC/CCS Calculations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Modeling\EPS\US\eps-us\InputData\ccs\CC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\ccs\CC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C8FFF93-ACC1-4A89-AA71-AD1CFE45439B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1F4816-9366-4DD5-A4A4-EAAECABEBF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="60840" yWindow="2385" windowWidth="24900" windowHeight="14490" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -62,6 +62,9 @@
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -69,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="106">
   <si>
     <t>Source:</t>
   </si>
@@ -375,6 +378,18 @@
   </si>
   <si>
     <t>low carbon hydrogen if</t>
+  </si>
+  <si>
+    <t>2026-10-02: the three CC-EUpT* tabs converted BTU per tonne CO2 to BTU per gram</t>
+  </si>
+  <si>
+    <t>by dividing by 10^12 (and the process tab also applied the 2020-&gt;2012 USD deflator</t>
+  </si>
+  <si>
+    <t>to energy). Corrected to /10^6 with no deflator; values rose ~1e6x, restoring the</t>
+  </si>
+  <si>
+    <t>capture energy penalty (cement: 8.70 BTU/g gas + 0.546 BTU/g electricity).</t>
   </si>
 </sst>
 </file>
@@ -760,60 +775,60 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="30.26953125" customWidth="1"/>
-    <col min="2" max="2" width="55.81640625" customWidth="1"/>
-    <col min="4" max="4" width="30.54296875" customWidth="1"/>
+    <col min="1" max="1" width="30.28515625" customWidth="1"/>
+    <col min="2" max="2" width="55.85546875" customWidth="1"/>
+    <col min="4" max="4" width="30.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>0</v>
       </c>
@@ -821,70 +836,70 @@
         <v>34</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>0.88711067149387013</v>
       </c>
@@ -892,12 +907,32 @@
         <v>84</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>3412141</v>
       </c>
       <c r="B30" t="s">
         <v>52</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -912,14 +947,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:M26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.7265625" customWidth="1"/>
-    <col min="2" max="2" width="42.54296875" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" customWidth="1"/>
+    <col min="2" max="2" width="42.5703125" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="58" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>95</v>
       </c>
@@ -960,20 +995,20 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A2,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>4.8431147099868251E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A2,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A2,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
-        <v>7.8700614037285907E-6</v>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A2,Data!$22:$22,0)),Data!$I$26)/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1003,20 +1038,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A3,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>4.8431147099868251E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A3,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A3,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
-        <v>7.8700614037285907E-6</v>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A3,Data!$22:$22,0)),Data!$I$26)/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1046,20 +1081,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A4,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>4.8431147099868251E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A4,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A4,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
-        <v>7.8700614037285907E-6</v>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A4,Data!$22:$22,0)),Data!$I$26)/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1089,20 +1124,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
       <c r="B5">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A5,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>4.8431147099868251E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A5,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A5,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
-        <v>7.8700614037285907E-6</v>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A5,Data!$22:$22,0)),Data!$I$26)/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1132,20 +1167,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
       <c r="B6">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A6,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>4.8431147099868251E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A6,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A6,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
-        <v>7.8700614037285907E-6</v>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A6,Data!$22:$22,0)),Data!$I$26)/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1175,20 +1210,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
       <c r="B7">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A7,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>4.8431147099868251E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A7,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A7,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
-        <v>7.8700614037285907E-6</v>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A7,Data!$22:$22,0)),Data!$I$26)/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1218,20 +1253,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
       <c r="B8">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A8,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>4.8431147099868251E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A8,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A8,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
-        <v>7.8700614037285907E-6</v>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A8,Data!$22:$22,0)),Data!$I$26)/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1261,20 +1296,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
       <c r="B9">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A9,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>4.8431147099868251E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A9,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A9,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
-        <v>7.8700614037285907E-6</v>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A9,Data!$22:$22,0)),Data!$I$26)/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1304,13 +1339,13 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
       <c r="B10">
         <f>B9</f>
-        <v>4.8431147099868251E-7</v>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C10">
         <f t="shared" ref="C10:D10" si="0">C9</f>
@@ -1318,7 +1353,7 @@
       </c>
       <c r="D10">
         <f t="shared" si="0"/>
-        <v>7.8700614037285907E-6</v>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1348,19 +1383,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
       <c r="B11">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A11,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>3.6323360324901186E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A11,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.40945692</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A11,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A11,Data!$22:$22,0)),Data!$I$26)/10^6</f>
         <v>0</v>
       </c>
       <c r="E11">
@@ -1391,20 +1426,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
       <c r="B12">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A12,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>4.8431147099868251E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A12,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A12,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
-        <v>7.8700614037285907E-6</v>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A12,Data!$22:$22,0)),Data!$I$26)/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1434,20 +1469,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
       <c r="B13">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A13,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>4.8431147099868251E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A13,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A13,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
-        <v>7.8700614037285907E-6</v>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A13,Data!$22:$22,0)),Data!$I$26)/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1477,20 +1512,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
       <c r="B14">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A14,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>4.8431147099868251E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A14,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A14,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
-        <v>7.7187140690415008E-6</v>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A14,Data!$22:$22,0)),Data!$I$26)/10^6</f>
+        <v>8.7009595499999985</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1520,20 +1555,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
       <c r="B15">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A15,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>4.8431147099868251E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A15,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A15,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
-        <v>7.7187140690415008E-6</v>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A15,Data!$22:$22,0)),Data!$I$26)/10^6</f>
+        <v>8.7009595499999985</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1563,20 +1598,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
       <c r="B16">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A16,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>4.8431147099868251E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A16,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A16,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
-        <v>7.8700614037285907E-6</v>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A16,Data!$22:$22,0)),Data!$I$26)/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1606,20 +1641,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
       <c r="B17">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A17,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>4.8431147099868251E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A17,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A17,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
-        <v>7.8700614037285907E-6</v>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A17,Data!$22:$22,0)),Data!$I$26)/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1649,20 +1684,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
       <c r="B18">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A18,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>4.8431147099868251E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A18,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A18,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
-        <v>7.8700614037285907E-6</v>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A18,Data!$22:$22,0)),Data!$I$26)/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1692,20 +1727,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>26</v>
       </c>
       <c r="B19">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A19,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>4.8431147099868251E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A19,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A19,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
-        <v>7.8700614037285907E-6</v>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A19,Data!$22:$22,0)),Data!$I$26)/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1735,20 +1770,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>27</v>
       </c>
       <c r="B20">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A20,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>4.8431147099868251E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A20,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A20,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
-        <v>7.8700614037285907E-6</v>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A20,Data!$22:$22,0)),Data!$I$26)/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1778,20 +1813,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>28</v>
       </c>
       <c r="B21">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A21,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>4.8431147099868251E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A21,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A21,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
-        <v>7.8700614037285907E-6</v>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A21,Data!$22:$22,0)),Data!$I$26)/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1821,20 +1856,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>29</v>
       </c>
       <c r="B22">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A22,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>4.8431147099868251E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A22,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A22,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
-        <v>7.8700614037285907E-6</v>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A22,Data!$22:$22,0)),Data!$I$26)/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1864,20 +1899,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>30</v>
       </c>
       <c r="B23">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A23,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>4.8431147099868251E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A23,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A23,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
-        <v>7.8700614037285907E-6</v>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A23,Data!$22:$22,0)),Data!$I$26)/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1907,19 +1942,19 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>31</v>
       </c>
       <c r="B24">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A24,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>3.0269466937417661E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A24,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.34121410000000002</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A24,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A24,Data!$22:$22,0)),Data!$I$26)/10^6</f>
         <v>0</v>
       </c>
       <c r="E24">
@@ -1950,20 +1985,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>32</v>
       </c>
       <c r="B25">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A25,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>4.8431147099868251E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A25,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A25,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
-        <v>7.8700614037285907E-6</v>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A25,Data!$22:$22,0)),Data!$I$26)/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1993,20 +2028,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>33</v>
       </c>
       <c r="B26">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A26,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>4.8431147099868251E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A26,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A26,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
-        <v>7.8700614037285907E-6</v>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A26,Data!$22:$22,0)),Data!$I$26)/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -2047,13 +2082,13 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:K13"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.7265625" customWidth="1"/>
-    <col min="2" max="2" width="42.54296875" customWidth="1"/>
+    <col min="1" max="1" width="26.7109375" customWidth="1"/>
+    <col min="2" max="2" width="42.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
         <v>95</v>
       </c>
@@ -2067,16 +2102,16 @@
       <c r="J1" s="7"/>
       <c r="K1" s="7"/>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>85</v>
       </c>
       <c r="B2">
-        <f>Data!E25/10^12</f>
-        <v>6.1418537999999999E-7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+        <f>Data!E25/10^6</f>
+        <v>0.61418538</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>86</v>
       </c>
@@ -2084,16 +2119,16 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>87</v>
       </c>
       <c r="B4">
-        <f>Data!E26/10^12</f>
-        <v>8.7009595499999985E-6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+        <f>Data!E26/10^6</f>
+        <v>8.7009595499999985</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>88</v>
       </c>
@@ -2101,7 +2136,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>89</v>
       </c>
@@ -2109,7 +2144,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
         <v>90</v>
       </c>
@@ -2117,7 +2152,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>91</v>
       </c>
@@ -2125,7 +2160,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
         <v>92</v>
       </c>
@@ -2133,7 +2168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>93</v>
       </c>
@@ -2141,7 +2176,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="7" t="s">
         <v>94</v>
       </c>
@@ -2149,7 +2184,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" s="7" t="s">
         <v>100</v>
       </c>
@@ -2157,7 +2192,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
         <v>101</v>
       </c>
@@ -2174,18 +2209,18 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA25B772-A559-4F07-971A-AC3B6FFE9BE6}">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:I30"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="34.81640625" customWidth="1"/>
+    <col min="1" max="1" width="34.85546875" customWidth="1"/>
     <col min="2" max="9" width="31" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -2214,7 +2249,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>39</v>
       </c>
@@ -2243,7 +2278,7 @@
         <v>259016</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -2272,7 +2307,7 @@
         <v>91.77</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -2301,7 +2336,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>43</v>
       </c>
@@ -2330,7 +2365,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>44</v>
       </c>
@@ -2359,7 +2394,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>45</v>
       </c>
@@ -2388,12 +2423,12 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>37</v>
       </c>
@@ -2430,7 +2465,7 @@
         <v>Industrial Furnace</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>39</v>
       </c>
@@ -2467,7 +2502,7 @@
         <v>259016</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>40</v>
       </c>
@@ -2496,7 +2531,7 @@
         <v>152.94</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>42</v>
       </c>
@@ -2533,7 +2568,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -2570,7 +2605,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -2607,7 +2642,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -2644,12 +2679,12 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" t="s">
         <v>31</v>
@@ -2667,7 +2702,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="B23" t="str">
         <f>B3</f>
         <v>Natural Gas Processing</v>
@@ -2701,7 +2736,7 @@
         <v>Industrial Furnace</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>48</v>
       </c>
@@ -2738,7 +2773,7 @@
         <v>571.58457392593505</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>49</v>
       </c>
@@ -2775,7 +2810,7 @@
         <v>545942.56000000006</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>50</v>
       </c>
@@ -2812,7 +2847,7 @@
         <v>8871566.5999999996</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>51</v>
       </c>
@@ -2849,12 +2884,12 @@
         <v>22.863382957037402</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>97</v>
       </c>
@@ -2870,18 +2905,18 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.453125" customWidth="1"/>
-    <col min="2" max="2" width="24.54296875" customWidth="1"/>
+    <col min="1" max="1" width="44.42578125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -2890,7 +2925,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -2899,7 +2934,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -2908,7 +2943,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -2917,7 +2952,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -2926,7 +2961,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -2935,7 +2970,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -2944,7 +2979,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -2953,7 +2988,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -2962,7 +2997,7 @@
         <v>442.08384092059458</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -2971,7 +3006,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -2980,7 +3015,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -2989,7 +3024,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -2998,7 +3033,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -3007,7 +3042,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -3016,7 +3051,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -3025,7 +3060,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -3034,7 +3069,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -3043,7 +3078,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -3052,7 +3087,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -3061,7 +3096,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -3070,7 +3105,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -3079,7 +3114,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -3088,7 +3123,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -3097,7 +3132,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -3117,18 +3152,18 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.453125" customWidth="1"/>
-    <col min="2" max="2" width="24.54296875" customWidth="1"/>
+    <col min="1" max="1" width="44.42578125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3137,7 +3172,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -3146,7 +3181,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -3155,7 +3190,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -3164,7 +3199,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -3173,7 +3208,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -3182,7 +3217,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -3191,7 +3226,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -3200,7 +3235,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -3209,7 +3244,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -3218,7 +3253,7 @@
         <v>80.122912914199276</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -3227,7 +3262,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -3236,7 +3271,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -3245,7 +3280,7 @@
         <v>214.0302346757544</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -3254,7 +3289,7 @@
         <v>157.60743456534033</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -3263,7 +3298,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -3272,7 +3307,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -3281,7 +3316,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -3290,7 +3325,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -3299,7 +3334,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -3308,7 +3343,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -3317,7 +3352,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -3326,7 +3361,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -3335,7 +3370,7 @@
         <v>85.494272870387022</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -3344,7 +3379,7 @@
         <v>507.0587751909739</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -3364,18 +3399,18 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="44.453125" customWidth="1"/>
-    <col min="2" max="2" width="24.54296875" customWidth="1"/>
+    <col min="1" max="1" width="44.42578125" customWidth="1"/>
+    <col min="2" max="2" width="24.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -3384,76 +3419,76 @@
         <v>210.77627576977025</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="3"/>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B7" s="3"/>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B8" s="3"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B9" s="3"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B10" s="3"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B11" s="3"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B12" s="3"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B13" s="3"/>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B14" s="3"/>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B15" s="3"/>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B16" s="3"/>
     </row>
-    <row r="17" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="3"/>
     </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="3"/>
     </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="3"/>
     </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="3"/>
     </row>
-    <row r="21" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="3"/>
     </row>
-    <row r="22" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="3"/>
     </row>
-    <row r="23" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B23" s="3"/>
     </row>
-    <row r="24" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="3"/>
     </row>
-    <row r="25" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B25" s="3"/>
     </row>
-    <row r="26" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" s="3"/>
     </row>
   </sheetData>
@@ -3467,18 +3502,18 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.1796875" customWidth="1"/>
-    <col min="2" max="2" width="25.81640625" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3487,7 +3522,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -3496,7 +3531,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -3505,7 +3540,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -3514,7 +3549,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -3523,7 +3558,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -3532,7 +3567,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -3541,7 +3576,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -3550,7 +3585,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -3559,7 +3594,7 @@
         <v>17.683353636823785</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -3568,7 +3603,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -3577,7 +3612,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -3586,7 +3621,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -3595,7 +3630,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -3604,7 +3639,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -3613,7 +3648,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -3622,7 +3657,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -3631,7 +3666,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -3640,7 +3675,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -3649,7 +3684,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -3658,7 +3693,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -3667,7 +3702,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -3676,7 +3711,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -3685,7 +3720,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -3694,7 +3729,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -3714,18 +3749,18 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.1796875" customWidth="1"/>
-    <col min="2" max="2" width="25.81640625" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -3734,7 +3769,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -3743,7 +3778,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -3752,7 +3787,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -3761,7 +3796,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -3770,7 +3805,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -3779,7 +3814,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -3788,7 +3823,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -3797,7 +3832,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -3806,7 +3841,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -3815,7 +3850,7 @@
         <v>5.6086039039939504</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -3824,7 +3859,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -3833,7 +3868,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -3842,7 +3877,7 @@
         <v>14.98211642730281</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -3851,7 +3886,7 @@
         <v>7.8803717282670158</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -3860,7 +3895,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -3869,7 +3904,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -3878,7 +3913,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -3887,7 +3922,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -3896,7 +3931,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -3905,7 +3940,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -3914,7 +3949,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -3923,7 +3958,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -3932,7 +3967,7 @@
         <v>5.1296563722232209</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -3941,7 +3976,7 @@
         <v>20.282351007638955</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -3961,18 +3996,18 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.1796875" customWidth="1"/>
-    <col min="2" max="2" width="25.81640625" customWidth="1"/>
+    <col min="1" max="1" width="19.140625" customWidth="1"/>
+    <col min="2" max="2" width="25.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="29" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="30" x14ac:dyDescent="0.25">
       <c r="B1" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>79</v>
       </c>
@@ -3992,14 +4027,14 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:M26"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="46.81640625" customWidth="1"/>
-    <col min="2" max="2" width="13.453125" customWidth="1"/>
-    <col min="4" max="4" width="11.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="46.85546875" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="58" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>95</v>
       </c>
@@ -4040,20 +4075,20 @@
         <v>99</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2">
-        <f>Data!$I$25/10^12</f>
-        <v>5.4594256000000005E-7</v>
+        <f>Data!$I$25/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <f>Data!$I$26/10^12</f>
-        <v>8.8715665999999999E-6</v>
+        <f>Data!$I$26/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -4083,20 +4118,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3">
-        <f>Data!$I$25/10^12</f>
-        <v>5.4594256000000005E-7</v>
+        <f>Data!$I$25/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C3">
         <v>0</v>
       </c>
       <c r="D3">
-        <f>Data!$I$26/10^12</f>
-        <v>8.8715665999999999E-6</v>
+        <f>Data!$I$26/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -4126,20 +4161,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4">
-        <f>Data!$I$25/10^12</f>
-        <v>5.4594256000000005E-7</v>
+        <f>Data!$I$25/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C4">
         <v>0</v>
       </c>
       <c r="D4">
-        <f>Data!$I$26/10^12</f>
-        <v>8.8715665999999999E-6</v>
+        <f>Data!$I$26/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -4169,20 +4204,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
       <c r="B5">
-        <f>Data!$I$25/10^12</f>
-        <v>5.4594256000000005E-7</v>
+        <f>Data!$I$25/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <f>Data!$I$26/10^12</f>
-        <v>8.8715665999999999E-6</v>
+        <f>Data!$I$26/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -4212,20 +4247,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
       <c r="B6">
-        <f>Data!$I$25/10^12</f>
-        <v>5.4594256000000005E-7</v>
+        <f>Data!$I$25/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <f>Data!$I$26/10^12</f>
-        <v>8.8715665999999999E-6</v>
+        <f>Data!$I$26/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -4255,20 +4290,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
       <c r="B7">
-        <f>Data!$I$25/10^12</f>
-        <v>5.4594256000000005E-7</v>
+        <f>Data!$I$25/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
       <c r="D7">
-        <f>Data!$I$26/10^12</f>
-        <v>8.8715665999999999E-6</v>
+        <f>Data!$I$26/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -4298,20 +4333,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
       <c r="B8">
-        <f>Data!$I$25/10^12</f>
-        <v>5.4594256000000005E-7</v>
+        <f>Data!$I$25/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
       <c r="D8">
-        <f>Data!$I$26/10^12</f>
-        <v>8.8715665999999999E-6</v>
+        <f>Data!$I$26/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -4341,20 +4376,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
       <c r="B9">
-        <f>Data!$I$25/10^12</f>
-        <v>5.4594256000000005E-7</v>
+        <f>Data!$I$25/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
       <c r="D9">
-        <f>Data!$I$26/10^12</f>
-        <v>8.8715665999999999E-6</v>
+        <f>Data!$I$26/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -4384,20 +4419,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
       <c r="B10">
-        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A10,Data!$22:$22,0)),Data!$I$25)*About!$A$28/10^12</f>
-        <v>4.2377253712384721E-7</v>
+        <f>IFERROR(INDEX(Data!$25:$25,MATCH('CC-CCoIPCE'!A10,Data!$22:$22,0)),Data!$I$25)/10^6</f>
+        <v>0.47769974000000004</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10">
-        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A10,Data!$22:$22,0)),Data!$I$26)*About!$A$28/10^12</f>
-        <v>7.7187140690415008E-6</v>
+        <f>IFERROR(INDEX(Data!$26:$26,MATCH('CC-CCoIPCE'!A10,Data!$22:$22,0)),Data!$I$26)/10^6</f>
+        <v>8.7009595499999985</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -4427,20 +4462,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
       <c r="B11">
-        <f>Data!$I$25/10^12</f>
-        <v>5.4594256000000005E-7</v>
+        <f>Data!$I$25/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
       <c r="D11">
-        <f>Data!$I$26/10^12</f>
-        <v>8.8715665999999999E-6</v>
+        <f>Data!$I$26/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -4470,20 +4505,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
       <c r="B12">
-        <f>Data!$I$25/10^12</f>
-        <v>5.4594256000000005E-7</v>
+        <f>Data!$I$25/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
       <c r="D12">
-        <f>Data!$I$26/10^12</f>
-        <v>8.8715665999999999E-6</v>
+        <f>Data!$I$26/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -4513,20 +4548,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
       <c r="B13">
-        <f>Data!$I$25/10^12</f>
-        <v>5.4594256000000005E-7</v>
+        <f>Data!$I$25/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
       <c r="D13">
-        <f>Data!$I$26/10^12</f>
-        <v>8.8715665999999999E-6</v>
+        <f>Data!$I$26/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4556,20 +4591,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
       <c r="B14">
-        <f>Data!$I$25/10^12</f>
-        <v>5.4594256000000005E-7</v>
+        <f>Data!$I$25/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
       <c r="D14">
-        <f>Data!$I$26/10^12</f>
-        <v>8.8715665999999999E-6</v>
+        <f>Data!$I$26/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4599,20 +4634,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
       <c r="B15">
-        <f>Data!$I$25/10^12</f>
-        <v>5.4594256000000005E-7</v>
+        <f>Data!$I$25/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
       <c r="D15">
-        <f>Data!$I$26/10^12</f>
-        <v>8.8715665999999999E-6</v>
+        <f>Data!$I$26/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4642,20 +4677,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
       <c r="B16">
-        <f>Data!$I$25/10^12</f>
-        <v>5.4594256000000005E-7</v>
+        <f>Data!$I$25/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
       <c r="D16">
-        <f>Data!$I$26/10^12</f>
-        <v>8.8715665999999999E-6</v>
+        <f>Data!$I$26/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4685,20 +4720,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
       <c r="B17">
-        <f>Data!$I$25/10^12</f>
-        <v>5.4594256000000005E-7</v>
+        <f>Data!$I$25/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
       <c r="D17">
-        <f>Data!$I$26/10^12</f>
-        <v>8.8715665999999999E-6</v>
+        <f>Data!$I$26/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4728,20 +4763,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
       <c r="B18">
-        <f>Data!$I$25/10^12</f>
-        <v>5.4594256000000005E-7</v>
+        <f>Data!$I$25/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
       <c r="D18">
-        <f>Data!$I$26/10^12</f>
-        <v>8.8715665999999999E-6</v>
+        <f>Data!$I$26/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4771,20 +4806,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>26</v>
       </c>
       <c r="B19">
-        <f>Data!$I$25/10^12</f>
-        <v>5.4594256000000005E-7</v>
+        <f>Data!$I$25/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
       <c r="D19">
-        <f>Data!$I$26/10^12</f>
-        <v>8.8715665999999999E-6</v>
+        <f>Data!$I$26/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4814,20 +4849,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>27</v>
       </c>
       <c r="B20">
-        <f>Data!$I$25/10^12</f>
-        <v>5.4594256000000005E-7</v>
+        <f>Data!$I$25/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
       <c r="D20">
-        <f>Data!$I$26/10^12</f>
-        <v>8.8715665999999999E-6</v>
+        <f>Data!$I$26/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4857,20 +4892,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>28</v>
       </c>
       <c r="B21">
-        <f>Data!$I$25/10^12</f>
-        <v>5.4594256000000005E-7</v>
+        <f>Data!$I$25/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
       <c r="D21">
-        <f>Data!$I$26/10^12</f>
-        <v>8.8715665999999999E-6</v>
+        <f>Data!$I$26/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4900,20 +4935,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>29</v>
       </c>
       <c r="B22">
-        <f>Data!$I$25/10^12</f>
-        <v>5.4594256000000005E-7</v>
+        <f>Data!$I$25/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
       <c r="D22">
-        <f>Data!$I$26/10^12</f>
-        <v>8.8715665999999999E-6</v>
+        <f>Data!$I$26/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4943,20 +4978,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>30</v>
       </c>
       <c r="B23">
-        <f>Data!$I$25/10^12</f>
-        <v>5.4594256000000005E-7</v>
+        <f>Data!$I$25/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
       <c r="D23">
-        <f>Data!$I$26/10^12</f>
-        <v>8.8715665999999999E-6</v>
+        <f>Data!$I$26/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4986,20 +5021,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>31</v>
       </c>
       <c r="B24">
-        <f>Data!$I$25/10^12</f>
-        <v>5.4594256000000005E-7</v>
+        <f>Data!$I$25/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C24">
         <v>0</v>
       </c>
       <c r="D24">
-        <f>Data!$I$26/10^12</f>
-        <v>8.8715665999999999E-6</v>
+        <f>Data!$I$26/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -5029,20 +5064,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>32</v>
       </c>
       <c r="B25">
-        <f>Data!$I$25/10^12</f>
-        <v>5.4594256000000005E-7</v>
+        <f>Data!$I$25/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C25">
         <v>0</v>
       </c>
       <c r="D25">
-        <f>Data!$I$26/10^12</f>
-        <v>8.8715665999999999E-6</v>
+        <f>Data!$I$26/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -5072,20 +5107,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>33</v>
       </c>
       <c r="B26">
-        <f>Data!$I$25/10^12</f>
-        <v>5.4594256000000005E-7</v>
+        <f>Data!$I$25/10^6</f>
+        <v>0.54594256000000008</v>
       </c>
       <c r="C26">
         <v>0</v>
       </c>
       <c r="D26">
-        <f>Data!$I$26/10^12</f>
-        <v>8.8715665999999999E-6</v>
+        <f>Data!$I$26/10^6</f>
+        <v>8.8715665999999995</v>
       </c>
       <c r="E26">
         <v>0</v>

--- a/InputData/ccs/CC/CCS Calculations.xlsx
+++ b/InputData/ccs/CC/CCS Calculations.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\ccs\CC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F1F4816-9366-4DD5-A4A4-EAAECABEBF39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14E24DCE-7B3B-445E-85EC-50FEFC966062}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="5" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" firstSheet="6" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -72,7 +72,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="133">
   <si>
     <t>Source:</t>
   </si>
@@ -368,18 +368,6 @@
     <t>hydrogen electrolysis in our BAU case.</t>
   </si>
   <si>
-    <t>green hydrogen</t>
-  </si>
-  <si>
-    <t>low carbon hydrogen</t>
-  </si>
-  <si>
-    <t>green hydrogen if</t>
-  </si>
-  <si>
-    <t>low carbon hydrogen if</t>
-  </si>
-  <si>
     <t>2026-10-02: the three CC-EUpT* tabs converted BTU per tonne CO2 to BTU per gram</t>
   </si>
   <si>
@@ -390,6 +378,99 @@
   </si>
   <si>
     <t>capture energy penalty (cement: 8.70 BTU/g gas + 0.546 BTU/g electricity).</t>
+  </si>
+  <si>
+    <t>Hydrogen sector capture energy: NETL 2022 SMR with and without CCS (added 2026-10-23)</t>
+  </si>
+  <si>
+    <t>NETL, Comparison of Commercial, State-of-the-Art, Fossil-Based Hydrogen Production Technologies, DOE/NETL-2022/3241, April 2022, https://www.osti.gov/servlets/purl/1862910</t>
+  </si>
+  <si>
+    <t>Case 1 SMR, no capture</t>
+  </si>
+  <si>
+    <t>Case 2 SMR with CCS</t>
+  </si>
+  <si>
+    <t>Source / formula</t>
+  </si>
+  <si>
+    <t>Hydrogen production (kg/hr)</t>
+  </si>
+  <si>
+    <t>Exhibits 3-5 and 3-23</t>
+  </si>
+  <si>
+    <t>HHV thermal input, natural gas (kWt)</t>
+  </si>
+  <si>
+    <t>Auxiliary electricity load (kWe)</t>
+  </si>
+  <si>
+    <t>Exhibits 3-5 and 3-23: balance of plant (+ CO2 capture/removal auxiliaries + CO2 compression in Case 2)</t>
+  </si>
+  <si>
+    <t>CO2 product (kg carbon/hr)</t>
+  </si>
+  <si>
+    <t>Exhibit 3-26 carbon balance (overall capture 96.2%)</t>
+  </si>
+  <si>
+    <t>CO2 captured (tonne CO2/hr)</t>
+  </si>
+  <si>
+    <t>carbon x 44.01/12.011</t>
+  </si>
+  <si>
+    <t>Incremental natural gas for capture (BTU/hr)</t>
+  </si>
+  <si>
+    <t>(Case 2 - Case 1 thermal input) x BTU per kWh</t>
+  </si>
+  <si>
+    <t>Incremental electricity for capture (BTU/hr)</t>
+  </si>
+  <si>
+    <t>(Case 2 - Case 1 auxiliary load) x BTU per kWh</t>
+  </si>
+  <si>
+    <t>Natural gas per tonne CO2 captured (BTU/tonne)</t>
+  </si>
+  <si>
+    <t>Electricity per tonne CO2 captured (BTU/tonne)</t>
+  </si>
+  <si>
+    <t>Same hydrogen output in both cases, so the differences are the capture energy. NETL captures 96.2% of plant carbon (syngas and reformer flue gas); EPS captures CCP (0.85) of the production-gas CO2 and applies this per-tonne energy to it.</t>
+  </si>
+  <si>
+    <t>The NPC/Gaffney Cline hydrogen column above (2.55 MWh gas + 0.18 MWh electricity per tonne) is no longer used for the hydrogen sector: it implied ~+39% gas on an SMR, against ~+6% in NETL.</t>
+  </si>
+  <si>
+    <t>2026-10-23: CC Energy Use per Ton Hydrogen Sector CO2 Sequestered (CC-EUpTHSCS) now comes from NETL 2022</t>
+  </si>
+  <si>
+    <t>(Data rows 32-46): 1.16 BTU/g natural gas + 0.50 BTU/g electricity, replacing the NPC hydrogen-plant column</t>
+  </si>
+  <si>
+    <t>(8.70 + 0.61 BTU/g). The industry tabs are unchanged. EPS now also charges this energy at fuel prices in</t>
+  </si>
+  <si>
+    <t>CCS Cost per Ton Blue Hydrogen Produced (it was used physically but never costed).</t>
+  </si>
+  <si>
+    <t>2026-10-23: the (1 + tax rate) multiplier was removed. NPC's tax rate is an input to its levelized-cost calculation, not a markup on capital; rows 9 and 19 are kept for reference only.</t>
+  </si>
+  <si>
+    <t>2026-10-23: CapEx per annual tonne (Data row 24) no longer multiplies by (1 + tax rate). The gross-up came in</t>
+  </si>
+  <si>
+    <t>with the NPC data (e87c7c8a, 2023) without a stated rationale; NPC uses the tax rate inside its levelized</t>
+  </si>
+  <si>
+    <t>cost, and no other EPS sector marks up capital by an income-tax rate. CapEx and the O&amp;M derived from it</t>
+  </si>
+  <si>
+    <t>(Data row 27, a % of CapEx) fall by 1/1.21 for every industry and for the hydrogen sector.</t>
   </si>
 </sst>
 </file>
@@ -775,7 +856,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:B35"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="30.28515625" customWidth="1"/>
@@ -917,22 +998,62 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>105</v>
+        <v>101</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -946,7 +1067,7 @@
   <sheetPr codeName="Sheet11">
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
@@ -954,7 +1075,7 @@
     <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>95</v>
       </c>
@@ -988,14 +1109,8 @@
       <c r="K1" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="L1" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -1031,14 +1146,8 @@
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1074,14 +1183,8 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -1117,14 +1220,8 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -1160,14 +1257,8 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -1203,14 +1294,8 @@
       <c r="K6">
         <v>0</v>
       </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -1246,14 +1331,8 @@
       <c r="K7">
         <v>0</v>
       </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -1289,14 +1368,8 @@
       <c r="K8">
         <v>0</v>
       </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1332,14 +1405,8 @@
       <c r="K9">
         <v>0</v>
       </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -1376,14 +1443,8 @@
       <c r="K10">
         <v>0</v>
       </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -1419,14 +1480,8 @@
       <c r="K11">
         <v>0</v>
       </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1462,14 +1517,8 @@
       <c r="K12">
         <v>0</v>
       </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -1505,14 +1554,8 @@
       <c r="K13">
         <v>0</v>
       </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -1548,14 +1591,8 @@
       <c r="K14">
         <v>0</v>
       </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -1591,14 +1628,8 @@
       <c r="K15">
         <v>0</v>
       </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -1634,14 +1665,8 @@
       <c r="K16">
         <v>0</v>
       </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -1677,14 +1702,8 @@
       <c r="K17">
         <v>0</v>
       </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1720,14 +1739,8 @@
       <c r="K18">
         <v>0</v>
       </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -1763,14 +1776,8 @@
       <c r="K19">
         <v>0</v>
       </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -1806,14 +1813,8 @@
       <c r="K20">
         <v>0</v>
       </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -1849,14 +1850,8 @@
       <c r="K21">
         <v>0</v>
       </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -1892,14 +1887,8 @@
       <c r="K22">
         <v>0</v>
       </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -1935,14 +1924,8 @@
       <c r="K23">
         <v>0</v>
       </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -1978,14 +1961,8 @@
       <c r="K24">
         <v>0</v>
       </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -2021,14 +1998,8 @@
       <c r="K25">
         <v>0</v>
       </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -2062,12 +2033,6 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
         <v>0</v>
       </c>
     </row>
@@ -2081,7 +2046,7 @@
   <sheetPr codeName="Sheet13">
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
@@ -2107,8 +2072,8 @@
         <v>85</v>
       </c>
       <c r="B2">
-        <f>Data!E25/10^6</f>
-        <v>0.61418538</v>
+        <f>Data!C44/10^6</f>
+        <v>0.49698931409077751</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -2124,8 +2089,8 @@
         <v>87</v>
       </c>
       <c r="B4">
-        <f>Data!E26/10^6</f>
-        <v>8.7009595499999985</v>
+        <f>Data!C43/10^6</f>
+        <v>1.1575132989851586</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -2181,22 +2146,6 @@
         <v>94</v>
       </c>
       <c r="B11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="B13">
         <v>0</v>
       </c>
     </row>
@@ -2208,7 +2157,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA25B772-A559-4F07-971A-AC3B6FFE9BE6}">
   <sheetPr codeName="Sheet3"/>
-  <dimension ref="A1:I30"/>
+  <dimension ref="A1:J46"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34.85546875" customWidth="1"/>
@@ -2568,7 +2517,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>43</v>
       </c>
@@ -2605,7 +2554,7 @@
         <v>2.6</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>44</v>
       </c>
@@ -2642,7 +2591,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>45</v>
       </c>
@@ -2679,12 +2628,12 @@
         <v>0.21</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
       <c r="B22" t="s">
         <v>31</v>
@@ -2702,7 +2651,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="B23" t="str">
         <f>B3</f>
         <v>Natural Gas Processing</v>
@@ -2736,44 +2685,47 @@
         <v>Industrial Furnace</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>48</v>
       </c>
       <c r="B24">
-        <f>AVERAGE(B5,B15)*10^6/B14*(1+B19)</f>
-        <v>96.37385234743823</v>
+        <f>AVERAGE(B5,B15)*10^6/B14</f>
+        <v>79.647811857386969</v>
       </c>
       <c r="C24">
-        <f t="shared" ref="C24:I24" si="8">AVERAGE(C5,C15)*10^6/C14*(1+C19)</f>
-        <v>90.318959616700909</v>
+        <f>AVERAGE(C5,C15)*10^6/C14</f>
+        <v>74.643768278265213</v>
       </c>
       <c r="D24">
-        <f t="shared" si="8"/>
-        <v>86.245524017467261</v>
+        <f>AVERAGE(D5,D15)*10^6/D14</f>
+        <v>71.277292576419228</v>
       </c>
       <c r="E24">
-        <f t="shared" si="8"/>
-        <v>237.598625</v>
+        <f>AVERAGE(E5,E15)*10^6/E14</f>
+        <v>196.36250000000001</v>
       </c>
       <c r="F24">
-        <f t="shared" si="8"/>
-        <v>241.26666666666668</v>
+        <f>AVERAGE(F5,F15)*10^6/F14</f>
+        <v>199.39393939393941</v>
       </c>
       <c r="G24">
-        <f t="shared" si="8"/>
-        <v>498.34125</v>
+        <f>AVERAGE(G5,G15)*10^6/G14</f>
+        <v>411.85227272727275</v>
       </c>
       <c r="H24">
-        <f t="shared" si="8"/>
-        <v>177.6637793116993</v>
+        <f>AVERAGE(H5,H15)*10^6/H14</f>
+        <v>146.82956967909033</v>
       </c>
       <c r="I24">
-        <f t="shared" si="8"/>
-        <v>571.58457392593505</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+        <f>AVERAGE(I5,I15)*10^6/I14</f>
+        <v>472.38394539333473</v>
+      </c>
+      <c r="J24" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>49</v>
       </c>
@@ -2810,7 +2762,7 @@
         <v>545942.56000000006</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>50</v>
       </c>
@@ -2847,51 +2799,193 @@
         <v>8871566.5999999996</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>51</v>
       </c>
       <c r="B27">
         <f>AVERAGE(B8,B18)*B24</f>
-        <v>5.7824311408462936</v>
+        <v>4.7788687114432182</v>
       </c>
       <c r="C27">
-        <f t="shared" ref="C27:I27" si="9">AVERAGE(C8,C18)*C24</f>
-        <v>6.3223271731690645</v>
+        <f t="shared" ref="C27:I27" si="8">AVERAGE(C8,C18)*C24</f>
+        <v>5.2250637794785657</v>
       </c>
       <c r="D27">
-        <f t="shared" si="9"/>
-        <v>4.3122762008733631</v>
+        <f t="shared" si="8"/>
+        <v>3.5638646288209617</v>
       </c>
       <c r="E27">
-        <f t="shared" si="9"/>
-        <v>11.87993125</v>
+        <f t="shared" si="8"/>
+        <v>9.818125000000002</v>
       </c>
       <c r="F27">
-        <f t="shared" si="9"/>
-        <v>16.888666666666669</v>
+        <f t="shared" si="8"/>
+        <v>13.957575757575759</v>
       </c>
       <c r="G27">
-        <f t="shared" si="9"/>
-        <v>19.93365</v>
+        <f t="shared" si="8"/>
+        <v>16.474090909090911</v>
       </c>
       <c r="H27">
-        <f t="shared" si="9"/>
-        <v>8.8831889655849654</v>
+        <f t="shared" si="8"/>
+        <v>7.3414784839545169</v>
       </c>
       <c r="I27">
-        <f t="shared" si="9"/>
-        <v>22.863382957037402</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
+        <f t="shared" si="8"/>
+        <v>18.895357815733391</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>97</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>104</v>
+      </c>
+      <c r="C35" t="s">
+        <v>105</v>
+      </c>
+      <c r="D35" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>107</v>
+      </c>
+      <c r="B36">
+        <v>20126</v>
+      </c>
+      <c r="C36">
+        <v>20125</v>
+      </c>
+      <c r="D36" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>109</v>
+      </c>
+      <c r="B37">
+        <v>1031068</v>
+      </c>
+      <c r="C37">
+        <v>1096328</v>
+      </c>
+      <c r="D37" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>110</v>
+      </c>
+      <c r="B38">
+        <v>12650</v>
+      </c>
+      <c r="C38">
+        <f>6710+16460+17500</f>
+        <v>40670</v>
+      </c>
+      <c r="D38" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>112</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39">
+        <v>52502</v>
+      </c>
+      <c r="D39" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>114</v>
+      </c>
+      <c r="C40">
+        <f>C39*44.01/12.011/1000</f>
+        <v>192.37474148697027</v>
+      </c>
+      <c r="D40" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>116</v>
+      </c>
+      <c r="C41">
+        <f>(C37-B37)*About!$A$30/1000</f>
+        <v>222676321.66</v>
+      </c>
+      <c r="D41" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>118</v>
+      </c>
+      <c r="C42">
+        <f>(C38-B38)*About!$A$30/1000</f>
+        <v>95608190.819999993</v>
+      </c>
+      <c r="D42" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>120</v>
+      </c>
+      <c r="C43">
+        <f>C41/C40</f>
+        <v>1157513.2989851586</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>121</v>
+      </c>
+      <c r="C44">
+        <f>C42/C40</f>
+        <v>496989.31409077754</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>
@@ -2922,7 +3016,7 @@
       </c>
       <c r="B2" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -2931,7 +3025,7 @@
       </c>
       <c r="B3" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2940,7 +3034,7 @@
       </c>
       <c r="B4" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -2949,7 +3043,7 @@
       </c>
       <c r="B5" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2958,7 +3052,7 @@
       </c>
       <c r="B6" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -2967,7 +3061,7 @@
       </c>
       <c r="B7" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -2976,7 +3070,7 @@
       </c>
       <c r="B8" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -2985,7 +3079,7 @@
       </c>
       <c r="B9" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -2994,7 +3088,7 @@
       </c>
       <c r="B10" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A10,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>442.08384092059458</v>
+        <v>365.35854621536748</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -3003,7 +3097,7 @@
       </c>
       <c r="B11" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -3012,7 +3106,7 @@
       </c>
       <c r="B12" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -3021,7 +3115,7 @@
       </c>
       <c r="B13" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -3030,7 +3124,7 @@
       </c>
       <c r="B14" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -3039,7 +3133,7 @@
       </c>
       <c r="B15" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -3048,7 +3142,7 @@
       </c>
       <c r="B16" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -3057,7 +3151,7 @@
       </c>
       <c r="B17" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -3066,7 +3160,7 @@
       </c>
       <c r="B18" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3075,7 +3169,7 @@
       </c>
       <c r="B19" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -3084,7 +3178,7 @@
       </c>
       <c r="B20" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3093,7 +3187,7 @@
       </c>
       <c r="B21" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -3102,7 +3196,7 @@
       </c>
       <c r="B22" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -3111,7 +3205,7 @@
       </c>
       <c r="B23" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -3120,7 +3214,7 @@
       </c>
       <c r="B24" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -3129,7 +3223,7 @@
       </c>
       <c r="B25" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -3138,7 +3232,7 @@
       </c>
       <c r="B26" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
   </sheetData>
@@ -3169,7 +3263,7 @@
       </c>
       <c r="B2" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A2,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3178,7 +3272,7 @@
       </c>
       <c r="B3" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A3,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3187,7 +3281,7 @@
       </c>
       <c r="B4" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A4,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3196,7 +3290,7 @@
       </c>
       <c r="B5" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A5,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -3205,7 +3299,7 @@
       </c>
       <c r="B6" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A6,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -3214,7 +3308,7 @@
       </c>
       <c r="B7" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A7,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3223,7 +3317,7 @@
       </c>
       <c r="B8" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A8,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -3232,7 +3326,7 @@
       </c>
       <c r="B9" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A9,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -3241,7 +3335,7 @@
       </c>
       <c r="B10" s="3">
         <f>Data!$I$24*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -3250,7 +3344,7 @@
       </c>
       <c r="B11" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A11,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>80.122912914199276</v>
+        <v>66.217283400164689</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -3259,7 +3353,7 @@
       </c>
       <c r="B12" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A12,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -3268,7 +3362,7 @@
       </c>
       <c r="B13" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A13,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -3277,7 +3371,7 @@
       </c>
       <c r="B14" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A14,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>214.0302346757544</v>
+        <v>176.88449146756562</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -3286,7 +3380,7 @@
       </c>
       <c r="B15" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A15,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>157.60743456534033</v>
+        <v>130.25407815317382</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -3295,7 +3389,7 @@
       </c>
       <c r="B16" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A16,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -3304,7 +3398,7 @@
       </c>
       <c r="B17" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A17,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -3313,7 +3407,7 @@
       </c>
       <c r="B18" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A18,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3322,7 +3416,7 @@
       </c>
       <c r="B19" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A19,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -3331,7 +3425,7 @@
       </c>
       <c r="B20" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A20,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3340,7 +3434,7 @@
       </c>
       <c r="B21" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A21,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -3349,7 +3443,7 @@
       </c>
       <c r="B22" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A22,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -3358,7 +3452,7 @@
       </c>
       <c r="B23" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A23,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -3367,7 +3461,7 @@
       </c>
       <c r="B24" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A24,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>85.494272870387022</v>
+        <v>70.656423859823988</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -3376,7 +3470,7 @@
       </c>
       <c r="B25" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A25,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -3385,7 +3479,7 @@
       </c>
       <c r="B26" s="3">
         <f>IFERROR(INDEX(Data!$24:$24,MATCH('CC-CCoIPCE'!A26,Data!$22:$22,0)),Data!$I$24)*About!$A$28</f>
-        <v>507.0587751909739</v>
+        <v>419.05683900080487</v>
       </c>
     </row>
   </sheetData>
@@ -3416,7 +3510,7 @@
       </c>
       <c r="B2" s="3">
         <f>Data!E24*About!$A$28</f>
-        <v>210.77627576977025</v>
+        <v>174.19526923121509</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3519,7 +3613,7 @@
       </c>
       <c r="B2">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3528,7 +3622,7 @@
       </c>
       <c r="B3">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3537,7 +3631,7 @@
       </c>
       <c r="B4">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3546,7 +3640,7 @@
       </c>
       <c r="B5">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -3555,7 +3649,7 @@
       </c>
       <c r="B6">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -3564,7 +3658,7 @@
       </c>
       <c r="B7">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3573,7 +3667,7 @@
       </c>
       <c r="B8">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -3582,7 +3676,7 @@
       </c>
       <c r="B9">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -3591,7 +3685,7 @@
       </c>
       <c r="B10">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A10,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>17.683353636823785</v>
+        <v>14.6143418486147</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -3600,7 +3694,7 @@
       </c>
       <c r="B11">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -3609,7 +3703,7 @@
       </c>
       <c r="B12">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -3618,7 +3712,7 @@
       </c>
       <c r="B13">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -3627,7 +3721,7 @@
       </c>
       <c r="B14">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -3636,7 +3730,7 @@
       </c>
       <c r="B15">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -3645,7 +3739,7 @@
       </c>
       <c r="B16">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -3654,7 +3748,7 @@
       </c>
       <c r="B17">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -3663,7 +3757,7 @@
       </c>
       <c r="B18">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3672,7 +3766,7 @@
       </c>
       <c r="B19">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -3681,7 +3775,7 @@
       </c>
       <c r="B20">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3690,7 +3784,7 @@
       </c>
       <c r="B21">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -3699,7 +3793,7 @@
       </c>
       <c r="B22">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -3708,7 +3802,7 @@
       </c>
       <c r="B23">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -3717,7 +3811,7 @@
       </c>
       <c r="B24">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -3726,7 +3820,7 @@
       </c>
       <c r="B25">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -3735,7 +3829,7 @@
       </c>
       <c r="B26">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
   </sheetData>
@@ -3766,7 +3860,7 @@
       </c>
       <c r="B2">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A2,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
@@ -3775,7 +3869,7 @@
       </c>
       <c r="B3">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A3,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -3784,7 +3878,7 @@
       </c>
       <c r="B4">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A4,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3793,7 +3887,7 @@
       </c>
       <c r="B5">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A5,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -3802,7 +3896,7 @@
       </c>
       <c r="B6">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A6,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -3811,7 +3905,7 @@
       </c>
       <c r="B7">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A7,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
@@ -3820,7 +3914,7 @@
       </c>
       <c r="B8">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A8,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
@@ -3829,7 +3923,7 @@
       </c>
       <c r="B9">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A9,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -3838,7 +3932,7 @@
       </c>
       <c r="B10">
         <f>Data!$I$27*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -3847,7 +3941,7 @@
       </c>
       <c r="B11">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A11,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>5.6086039039939504</v>
+        <v>4.6352098380115292</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
@@ -3856,7 +3950,7 @@
       </c>
       <c r="B12">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A12,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -3865,7 +3959,7 @@
       </c>
       <c r="B13">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A13,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
@@ -3874,7 +3968,7 @@
       </c>
       <c r="B14">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A14,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>14.98211642730281</v>
+        <v>12.381914402729594</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
@@ -3883,7 +3977,7 @@
       </c>
       <c r="B15">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A15,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>7.8803717282670158</v>
+        <v>6.5127039076586914</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -3892,7 +3986,7 @@
       </c>
       <c r="B16">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A16,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
@@ -3901,7 +3995,7 @@
       </c>
       <c r="B17">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A17,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
@@ -3910,7 +4004,7 @@
       </c>
       <c r="B18">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A18,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3919,7 +4013,7 @@
       </c>
       <c r="B19">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A19,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -3928,7 +4022,7 @@
       </c>
       <c r="B20">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A20,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
@@ -3937,7 +4031,7 @@
       </c>
       <c r="B21">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A21,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
@@ -3946,7 +4040,7 @@
       </c>
       <c r="B22">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A22,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
@@ -3955,7 +4049,7 @@
       </c>
       <c r="B23">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A23,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -3964,7 +4058,7 @@
       </c>
       <c r="B24">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A24,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>5.1296563722232209</v>
+        <v>4.2393854315894393</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
@@ -3973,7 +4067,7 @@
       </c>
       <c r="B25">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A25,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
@@ -3982,7 +4076,7 @@
       </c>
       <c r="B26">
         <f>IFERROR(INDEX(Data!$27:$27,MATCH('CC-CCoIPCE'!A26,Data!$22:$22,0)),Data!$I$27)*About!$A$28</f>
-        <v>20.282351007638955</v>
+        <v>16.762273560032195</v>
       </c>
     </row>
   </sheetData>
@@ -4013,7 +4107,7 @@
       </c>
       <c r="B2">
         <f>Data!E27*About!$A$28</f>
-        <v>10.538813788488513</v>
+        <v>8.7097634615607546</v>
       </c>
     </row>
   </sheetData>
@@ -4026,7 +4120,7 @@
   <sheetPr codeName="Sheet10">
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:M26"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="46.85546875" customWidth="1"/>
@@ -4034,7 +4128,7 @@
     <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>95</v>
       </c>
@@ -4068,14 +4162,8 @@
       <c r="K1" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="L1" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>9</v>
       </c>
@@ -4111,14 +4199,8 @@
       <c r="K2">
         <v>0</v>
       </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="M2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -4154,14 +4236,8 @@
       <c r="K3">
         <v>0</v>
       </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -4197,14 +4273,8 @@
       <c r="K4">
         <v>0</v>
       </c>
-      <c r="L4">
-        <v>0</v>
-      </c>
-      <c r="M4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -4240,14 +4310,8 @@
       <c r="K5">
         <v>0</v>
       </c>
-      <c r="L5">
-        <v>0</v>
-      </c>
-      <c r="M5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -4283,14 +4347,8 @@
       <c r="K6">
         <v>0</v>
       </c>
-      <c r="L6">
-        <v>0</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>14</v>
       </c>
@@ -4326,14 +4384,8 @@
       <c r="K7">
         <v>0</v>
       </c>
-      <c r="L7">
-        <v>0</v>
-      </c>
-      <c r="M7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>15</v>
       </c>
@@ -4369,14 +4421,8 @@
       <c r="K8">
         <v>0</v>
       </c>
-      <c r="L8">
-        <v>0</v>
-      </c>
-      <c r="M8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -4412,14 +4458,8 @@
       <c r="K9">
         <v>0</v>
       </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>17</v>
       </c>
@@ -4455,14 +4495,8 @@
       <c r="K10">
         <v>0</v>
       </c>
-      <c r="L10">
-        <v>0</v>
-      </c>
-      <c r="M10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -4498,14 +4532,8 @@
       <c r="K11">
         <v>0</v>
       </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -4541,14 +4569,8 @@
       <c r="K12">
         <v>0</v>
       </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>20</v>
       </c>
@@ -4584,14 +4606,8 @@
       <c r="K13">
         <v>0</v>
       </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>21</v>
       </c>
@@ -4627,14 +4643,8 @@
       <c r="K14">
         <v>0</v>
       </c>
-      <c r="L14">
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -4670,14 +4680,8 @@
       <c r="K15">
         <v>0</v>
       </c>
-      <c r="L15">
-        <v>0</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>23</v>
       </c>
@@ -4713,14 +4717,8 @@
       <c r="K16">
         <v>0</v>
       </c>
-      <c r="L16">
-        <v>0</v>
-      </c>
-      <c r="M16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>24</v>
       </c>
@@ -4756,14 +4754,8 @@
       <c r="K17">
         <v>0</v>
       </c>
-      <c r="L17">
-        <v>0</v>
-      </c>
-      <c r="M17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -4799,14 +4791,8 @@
       <c r="K18">
         <v>0</v>
       </c>
-      <c r="L18">
-        <v>0</v>
-      </c>
-      <c r="M18">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>26</v>
       </c>
@@ -4842,14 +4828,8 @@
       <c r="K19">
         <v>0</v>
       </c>
-      <c r="L19">
-        <v>0</v>
-      </c>
-      <c r="M19">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>27</v>
       </c>
@@ -4885,14 +4865,8 @@
       <c r="K20">
         <v>0</v>
       </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>28</v>
       </c>
@@ -4928,14 +4902,8 @@
       <c r="K21">
         <v>0</v>
       </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -4971,14 +4939,8 @@
       <c r="K22">
         <v>0</v>
       </c>
-      <c r="L22">
-        <v>0</v>
-      </c>
-      <c r="M22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>30</v>
       </c>
@@ -5014,14 +4976,8 @@
       <c r="K23">
         <v>0</v>
       </c>
-      <c r="L23">
-        <v>0</v>
-      </c>
-      <c r="M23">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>31</v>
       </c>
@@ -5057,14 +5013,8 @@
       <c r="K24">
         <v>0</v>
       </c>
-      <c r="L24">
-        <v>0</v>
-      </c>
-      <c r="M24">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>32</v>
       </c>
@@ -5100,14 +5050,8 @@
       <c r="K25">
         <v>0</v>
       </c>
-      <c r="L25">
-        <v>0</v>
-      </c>
-      <c r="M25">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>33</v>
       </c>
@@ -5141,12 +5085,6 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>0</v>
-      </c>
-      <c r="L26">
-        <v>0</v>
-      </c>
-      <c r="M26">
         <v>0</v>
       </c>
     </row>
